--- a/Modelos/AP/FDMS/plano_trabalho_FDMS.xlsx
+++ b/Modelos/AP/FDMS/plano_trabalho_FDMS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pccli\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2E1ABC2-4678-4BB6-9EA0-0F2E06B6EF21}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3454F5DC-69C0-4AC6-B66F-C51B558346B6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16365" windowHeight="10380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7655,9 +7655,9 @@
       <c r="H50" s="190"/>
       <c r="I50" s="190"/>
       <c r="J50" s="181"/>
-      <c r="K50" s="222" t="e">
+      <c r="K50" s="222">
         <f>K81</f>
-        <v>#REF!</v>
+        <v>0</v>
       </c>
       <c r="L50" s="223"/>
       <c r="M50" s="1"/>
@@ -8073,9 +8073,9 @@
       <c r="H73" s="190"/>
       <c r="I73" s="190"/>
       <c r="J73" s="181"/>
-      <c r="K73" s="222" t="e">
-        <f>SUM(#REF!,#REF!,#REF!,#REF!,#REF!,#REF!,#REF!)</f>
-        <v>#REF!</v>
+      <c r="K73" s="222">
+        <f>SUM(K140,K146,K192,K200,K208,G138)</f>
+        <v>0</v>
       </c>
       <c r="L73" s="223"/>
       <c r="M73" s="1"/>
@@ -8190,9 +8190,9 @@
       <c r="H79" s="190"/>
       <c r="I79" s="190"/>
       <c r="J79" s="181"/>
-      <c r="K79" s="222" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
+      <c r="K79" s="222">
+        <f>K263</f>
+        <v>0</v>
       </c>
       <c r="L79" s="223"/>
       <c r="M79" s="1"/>
@@ -8229,9 +8229,9 @@
       <c r="H81" s="190"/>
       <c r="I81" s="190"/>
       <c r="J81" s="181"/>
-      <c r="K81" s="231" t="e">
+      <c r="K81" s="231">
         <f>SUM(K73:L80)</f>
-        <v>#REF!</v>
+        <v>0</v>
       </c>
       <c r="L81" s="223"/>
       <c r="M81" s="1"/>
